--- a/data/gravel/Binary Kinetik 2025.xlsx
+++ b/data/gravel/Binary Kinetik 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E9D684-C0BA-7F4E-B511-41E06798E066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8205235-CBDB-444E-AF05-A814F2BFBB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2440" yWindow="1020" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32880" yWindow="-18260" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,12 @@
   </si>
   <si>
     <t>a8:i32</t>
+  </si>
+  <si>
+    <t>15% sag</t>
+  </si>
+  <si>
+    <t>15% sagged 120 mm fork</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1180,12 @@
       <c r="I16" s="6">
         <v>512</v>
       </c>
-      <c r="J16" s="6"/>
+      <c r="J16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">

--- a/data/gravel/Binary Kinetik 2025.xlsx
+++ b/data/gravel/Binary Kinetik 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8205235-CBDB-444E-AF05-A814F2BFBB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9E6D19-DF19-C842-82D3-CC89604A0953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32880" yWindow="-18260" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40020" yWindow="-18340" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>15% sagged 120 mm fork</t>
+  </si>
+  <si>
+    <t>https://binarybicycles.com/wp-content/uploads/2025/10/titanium-Kinetik-bikepacking-bike-1062x800.jpg</t>
   </si>
 </sst>
 </file>
@@ -381,7 +384,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -403,13 +406,6 @@
       <sz val="14"/>
       <color rgb="FF313131"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="14"/>
-      <color theme="10"/>
-      <name val="Futura"/>
       <family val="2"/>
     </font>
     <font>
@@ -440,24 +436,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -794,8 +787,13 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -813,22 +811,22 @@
       <c r="B8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>15.5</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>16</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>17</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>18</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>19</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>20</v>
       </c>
       <c r="I8" s="2">
@@ -852,22 +850,22 @@
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>595</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>600</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>609</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>613</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>625</v>
       </c>
       <c r="H9">
@@ -889,22 +887,22 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>390</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>410</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>415</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>420</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>440</v>
       </c>
       <c r="H10">
@@ -931,22 +929,22 @@
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>74</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>74</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>74</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>74</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>74</v>
       </c>
       <c r="H11">
@@ -973,28 +971,28 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>100</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>100</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>100</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>110</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>130</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>145</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>160</v>
       </c>
       <c r="J12" s="3"/>
@@ -1015,22 +1013,22 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>67</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>67</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>67</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>67</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>67</v>
       </c>
       <c r="H13">
@@ -1039,7 +1037,7 @@
       <c r="I13" s="3">
         <v>67</v>
       </c>
-      <c r="J13" s="6"/>
+      <c r="J13" s="5"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -1057,7 +1055,7 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C14">
@@ -1099,7 +1097,7 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C15">
@@ -1142,13 +1140,13 @@
       <c r="M15" t="s">
         <v>105</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="N15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="O15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P15" s="6" t="s">
+      <c r="P15" s="5" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1156,7 +1154,7 @@
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>88</v>
       </c>
       <c r="C16">
@@ -1171,16 +1169,16 @@
       <c r="F16">
         <v>512</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>512</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>512</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>512</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="5" t="s">
         <v>112</v>
       </c>
       <c r="K16" s="1" t="s">
@@ -1191,7 +1189,7 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>89</v>
       </c>
       <c r="C17">
@@ -1222,19 +1220,19 @@
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="N17" s="5" t="s">
         <v>106</v>
       </c>
       <c r="O17" t="s">
@@ -1248,7 +1246,7 @@
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C18">
@@ -1282,7 +1280,7 @@
       <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>76</v>
       </c>
       <c r="C19">
@@ -1311,7 +1309,7 @@
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C20">
@@ -1346,7 +1344,7 @@
       <c r="C21">
         <v>702</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>707</v>
       </c>
       <c r="E21">
@@ -1548,31 +1546,31 @@
       <c r="A31" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="8">
         <f>C38</f>
         <v>154.60869565217391</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <f t="shared" ref="D31:I32" si="2">D38</f>
         <v>160.13043478260869</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="8">
         <f t="shared" si="2"/>
         <v>160.13043478260869</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="8">
         <f t="shared" si="2"/>
         <v>171.17391304347825</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="8">
         <f t="shared" si="2"/>
         <v>176.69565217391303</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="8">
         <f t="shared" si="2"/>
         <v>179.45652173913041</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="8">
         <f t="shared" si="2"/>
         <v>184.97826086956522</v>
       </c>
@@ -1586,50 +1584,50 @@
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <f>C39</f>
         <v>165.65217391304347</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <f t="shared" si="2"/>
         <v>171.17391304347825</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="8">
         <f t="shared" si="2"/>
         <v>173.93478260869566</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="8">
         <f t="shared" si="2"/>
         <v>179.45652173913041</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="8">
         <f t="shared" si="2"/>
         <v>184.97826086956522</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="8">
         <f t="shared" si="2"/>
         <v>187.7391304347826</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="8">
         <f t="shared" si="2"/>
         <v>193.2608695652174</v>
       </c>
       <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>102</v>
       </c>
       <c r="H33" t="s">
@@ -1638,7 +1636,7 @@
       <c r="I33" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="7" t="s">
+      <c r="J33" s="6" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1868,6 +1866,9 @@
       <c r="A42" t="s">
         <v>37</v>
       </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
@@ -1946,6 +1947,9 @@
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>47</v>
+      </c>
+      <c r="B53">
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Binary Kinetik 2025.xlsx
+++ b/data/gravel/Binary Kinetik 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9E6D19-DF19-C842-82D3-CC89604A0953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0300AEFD-41C1-7E45-A46D-CF7B5353724D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40020" yWindow="-18340" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35980" yWindow="-18340" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>https://binarybicycles.com/wp-content/uploads/2025/10/titanium-Kinetik-bikepacking-bike-1062x800.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Casa Grande, Arizona, USA</t>
   </si>
 </sst>
 </file>
@@ -745,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V72"/>
+  <dimension ref="A1:V73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2082,6 +2088,14 @@
         <v>84</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>114</v>
+      </c>
+      <c r="B73" t="s">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Binary Kinetik 2025.xlsx
+++ b/data/gravel/Binary Kinetik 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0300AEFD-41C1-7E45-A46D-CF7B5353724D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2E883B-9495-3449-84AA-FBCF58765645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35980" yWindow="-18340" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,24 @@
   </si>
   <si>
     <t>Casa Grande, Arizona, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -751,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1923,176 +1941,206 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>34</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
-      </c>
-      <c r="B53">
-        <v>38</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>47</v>
+      </c>
+      <c r="B59">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B63" s="1"/>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>34</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>34</v>
+        <v>57</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B69">
-        <v>2099</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75">
+        <v>2099</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>114</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>115</v>
       </c>
     </row>

--- a/data/gravel/Binary Kinetik 2025.xlsx
+++ b/data/gravel/Binary Kinetik 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2E883B-9495-3449-84AA-FBCF58765645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A201B27D-9C30-FB44-8788-9EDBD21DFA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35980" yWindow="-18340" windowWidth="25260" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32940" yWindow="-22820" windowWidth="28300" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="132">
   <si>
     <t>brand</t>
   </si>
@@ -365,12 +365,6 @@
     <t>flat bar</t>
   </si>
   <si>
-    <t>a8:i32</t>
-  </si>
-  <si>
-    <t>15% sag</t>
-  </si>
-  <si>
     <t>15% sagged 120 mm fork</t>
   </si>
   <si>
@@ -399,6 +393,42 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>S﻿</t>
+  </si>
+  <si>
+    <t>SMD﻿</t>
+  </si>
+  <si>
+    <t>M﻿</t>
+  </si>
+  <si>
+    <t>ML﻿</t>
+  </si>
+  <si>
+    <t>L﻿</t>
+  </si>
+  <si>
+    <t>XL﻿</t>
+  </si>
+  <si>
+    <t>29-31.5﻿</t>
+  </si>
+  <si>
+    <t>Dimensions are using an sagged 29er 120mm fork and 29 x 3.0 wheels and tires.</t>
+  </si>
+  <si>
+    <t>ZS44</t>
+  </si>
+  <si>
+    <t>EC44</t>
+  </si>
+  <si>
+    <t>a8:h32</t>
+  </si>
+  <si>
+    <t>SMD</t>
   </si>
 </sst>
 </file>
@@ -408,7 +438,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -442,6 +472,41 @@
       <color rgb="FF313131"/>
       <name val="Futura Medium"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Futura"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF20211C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF313131"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -463,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -471,8 +536,13 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,13 +839,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:W79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -783,7 +853,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -791,7 +861,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -799,15 +869,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4">
-        <v>45929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+        <v>45982</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -815,47 +885,45 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D8" s="5">
-        <v>16</v>
-      </c>
-      <c r="E8" s="6">
-        <v>17</v>
-      </c>
-      <c r="F8" s="6">
-        <v>18</v>
-      </c>
-      <c r="G8" s="6">
-        <v>19</v>
-      </c>
-      <c r="H8" s="6">
-        <v>20</v>
-      </c>
-      <c r="I8" s="2">
-        <v>21</v>
-      </c>
+      <c r="C8" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
@@ -868,73 +936,84 @@
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:23" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="5">
-        <v>595</v>
-      </c>
-      <c r="D9" s="5">
-        <v>600</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="C9" s="9">
+        <v>593</v>
+      </c>
+      <c r="D9" s="9">
         <v>609</v>
       </c>
-      <c r="F9" s="5">
+      <c r="E9" s="9">
         <v>613</v>
       </c>
-      <c r="G9" s="5">
+      <c r="F9" s="9">
         <v>625</v>
       </c>
-      <c r="H9">
+      <c r="G9" s="9">
         <v>638</v>
       </c>
-      <c r="I9" s="3">
+      <c r="H9" s="9">
         <v>651</v>
       </c>
+      <c r="I9" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Q9" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="T9" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="U9" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="V9" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="W9" s="11"/>
+    </row>
+    <row r="10" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="9">
         <v>390</v>
       </c>
-      <c r="D10" s="5">
-        <v>410</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="D10" s="9">
         <v>415</v>
       </c>
-      <c r="F10" s="5">
+      <c r="E10" s="9">
         <v>420</v>
       </c>
-      <c r="G10" s="5">
+      <c r="F10" s="9">
         <v>440</v>
       </c>
-      <c r="H10">
+      <c r="G10" s="9">
         <v>480</v>
       </c>
-      <c r="I10" s="3">
+      <c r="H10" s="9">
         <v>508</v>
       </c>
+      <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -942,41 +1021,54 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Q10" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="R10" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="S10" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="T10" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="W10" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="9">
         <v>74</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="9">
         <v>74</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="9">
         <v>74</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="9">
         <v>74</v>
       </c>
-      <c r="G11" s="5">
-        <v>74</v>
-      </c>
-      <c r="H11">
+      <c r="G11" s="9">
         <v>74.5</v>
       </c>
-      <c r="I11" s="3">
+      <c r="H11" s="9">
         <v>74.5</v>
       </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -984,41 +1076,33 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="9">
         <v>100</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="9">
         <v>100</v>
       </c>
-      <c r="E12" s="5">
-        <v>100</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="E12" s="9">
         <v>110</v>
       </c>
-      <c r="G12" s="5">
+      <c r="F12" s="9">
         <v>130</v>
       </c>
-      <c r="H12" s="5">
+      <c r="G12" s="9">
         <v>145</v>
       </c>
-      <c r="I12" s="5">
+      <c r="H12" s="9">
         <v>160</v>
       </c>
+      <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1026,83 +1110,67 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="9">
         <v>67</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="9">
         <v>67</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="9">
         <v>67</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="9">
         <v>67</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="9">
         <v>67</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="9">
         <v>67</v>
       </c>
-      <c r="I13" s="3">
-        <v>67</v>
-      </c>
-      <c r="J13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C14">
-        <v>65</v>
-      </c>
-      <c r="D14">
-        <v>65</v>
-      </c>
-      <c r="E14">
+      <c r="C14" s="9">
         <v>60</v>
       </c>
-      <c r="F14">
+      <c r="D14" s="9">
         <v>60</v>
       </c>
-      <c r="G14">
+      <c r="E14" s="9">
         <v>60</v>
       </c>
-      <c r="H14">
+      <c r="F14" s="9">
         <v>60</v>
       </c>
-      <c r="I14">
+      <c r="G14" s="9">
         <v>60</v>
       </c>
+      <c r="H14" s="9">
+        <v>60</v>
+      </c>
+      <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1110,139 +1178,123 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C15">
-        <f>VALUE(LEFT(J15,3))</f>
+      <c r="C15" s="9">
+        <f>VALUE(LEFT(I15,3))</f>
         <v>455</v>
       </c>
-      <c r="D15">
-        <f t="shared" ref="D15:I15" si="0">VALUE(LEFT(K15,3))</f>
+      <c r="D15" s="9">
+        <f t="shared" ref="D15:H15" si="0">VALUE(LEFT(J15,3))</f>
         <v>455</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>455</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="9">
         <f t="shared" si="0"/>
         <v>455</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="9">
         <f t="shared" si="0"/>
         <v>455</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="9">
         <f t="shared" si="0"/>
         <v>455</v>
       </c>
-      <c r="I15">
-        <f t="shared" si="0"/>
-        <v>455</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="I15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="K15" t="s">
+      <c r="J15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="L15" t="s">
+      <c r="K15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="M15" t="s">
+      <c r="L15" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="N15" s="5" t="s">
+      <c r="M15" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>105</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="P15" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="9">
         <v>512</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="9">
         <v>512</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="9">
         <v>512</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="9">
         <v>512</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="9">
         <v>512</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="9">
         <v>512</v>
       </c>
-      <c r="I16" s="5">
-        <v>512</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I16" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C17">
-        <f>VALUE(LEFT(J17,2))</f>
+      <c r="C17" s="9">
+        <f>VALUE(LEFT(I17,2))</f>
         <v>44</v>
       </c>
-      <c r="D17">
-        <f t="shared" ref="D17:I17" si="1">VALUE(LEFT(K17,2))</f>
+      <c r="D17" s="9">
+        <f t="shared" ref="D17:H17" si="1">VALUE(LEFT(J17,2))</f>
         <v>44</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="9">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="9">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="9">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="9">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>44</v>
+      <c r="I17" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>106</v>
@@ -1256,224 +1308,199 @@
       <c r="M17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="N17" s="5" t="s">
+      <c r="N17" t="s">
         <v>106</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C18">
-        <v>1149</v>
-      </c>
-      <c r="D18">
-        <v>1154</v>
-      </c>
-      <c r="E18">
+      <c r="C18" s="9">
+        <v>1151</v>
+      </c>
+      <c r="D18" s="9">
         <v>1167</v>
       </c>
-      <c r="F18">
-        <v>1171</v>
-      </c>
-      <c r="G18">
+      <c r="E18" s="9">
+        <v>1172</v>
+      </c>
+      <c r="F18" s="9">
         <v>1187</v>
       </c>
-      <c r="H18">
+      <c r="G18" s="9">
         <v>1208</v>
       </c>
-      <c r="I18">
+      <c r="H18" s="9">
         <v>1223</v>
       </c>
+      <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C19">
-        <v>611</v>
-      </c>
-      <c r="D19">
-        <v>611</v>
-      </c>
-      <c r="E19">
+      <c r="C19" s="9">
         <v>616</v>
       </c>
-      <c r="F19">
+      <c r="D19" s="9">
+        <v>616</v>
+      </c>
+      <c r="E19" s="9">
         <v>625</v>
       </c>
-      <c r="G19">
+      <c r="F19" s="9">
         <v>643</v>
       </c>
-      <c r="H19">
+      <c r="G19" s="9">
         <v>657</v>
       </c>
-      <c r="I19">
+      <c r="H19" s="9">
         <v>671</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C20">
-        <v>419</v>
-      </c>
-      <c r="D20">
-        <v>424</v>
-      </c>
-      <c r="E20">
+      <c r="C20" s="9">
+        <v>417</v>
+      </c>
+      <c r="D20" s="9">
         <v>433</v>
       </c>
-      <c r="F20">
+      <c r="E20" s="9">
         <v>434</v>
       </c>
-      <c r="G20">
-        <v>440</v>
-      </c>
-      <c r="H20">
+      <c r="F20" s="9">
+        <v>441</v>
+      </c>
+      <c r="G20" s="9">
         <v>456</v>
       </c>
-      <c r="I20">
+      <c r="H20" s="9">
         <v>465</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C21">
-        <v>702</v>
-      </c>
-      <c r="D21" s="7">
-        <v>707</v>
-      </c>
-      <c r="E21">
+      <c r="C21" s="9">
+        <v>703</v>
+      </c>
+      <c r="D21" s="9">
         <v>719</v>
       </c>
-      <c r="F21">
+      <c r="E21" s="9">
         <v>724</v>
       </c>
-      <c r="G21">
+      <c r="F21" s="9">
         <v>738</v>
       </c>
-      <c r="H21">
+      <c r="G21" s="9">
         <v>759</v>
       </c>
-      <c r="I21">
+      <c r="H21" s="9">
         <v>774</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="9">
         <v>771</v>
       </c>
-      <c r="D22">
-        <v>781</v>
-      </c>
-      <c r="E22">
+      <c r="D22" s="9">
         <v>792</v>
       </c>
-      <c r="F22">
+      <c r="E22" s="9">
         <v>821</v>
       </c>
-      <c r="G22">
+      <c r="F22" s="9">
         <v>840</v>
       </c>
-      <c r="H22">
+      <c r="G22" s="9">
         <v>867</v>
       </c>
-      <c r="I22" s="2">
+      <c r="H22" s="9">
         <v>887</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>17</v>
       </c>
+      <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H24">
-        <v>2550</v>
-      </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="2"/>
+      <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="2"/>
+      <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="I27" s="2"/>
+      <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -1495,16 +1522,13 @@
       <c r="H28">
         <v>700</v>
       </c>
-      <c r="I28">
-        <v>700</v>
-      </c>
+      <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -1526,16 +1550,13 @@
       <c r="H29">
         <v>3</v>
       </c>
-      <c r="I29">
-        <v>3</v>
-      </c>
+      <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -1557,88 +1578,77 @@
       <c r="H30">
         <v>3</v>
       </c>
-      <c r="I30">
-        <v>3</v>
-      </c>
+      <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <f>C38</f>
         <v>154.60869565217391</v>
       </c>
-      <c r="D31" s="8">
-        <f t="shared" ref="D31:I32" si="2">D38</f>
+      <c r="D31" s="7">
+        <f t="shared" ref="D31:H32" si="2">D38</f>
         <v>160.13043478260869</v>
       </c>
-      <c r="E31" s="8">
-        <f t="shared" si="2"/>
-        <v>160.13043478260869</v>
-      </c>
-      <c r="F31" s="8">
+      <c r="E31" s="7">
         <f t="shared" si="2"/>
         <v>171.17391304347825</v>
       </c>
-      <c r="G31" s="8">
+      <c r="F31" s="7">
         <f t="shared" si="2"/>
         <v>176.69565217391303</v>
       </c>
-      <c r="H31" s="8">
+      <c r="G31" s="7">
         <f t="shared" si="2"/>
         <v>179.45652173913041</v>
       </c>
-      <c r="I31" s="8">
+      <c r="H31" s="7">
         <f t="shared" si="2"/>
         <v>184.97826086956522</v>
       </c>
+      <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <f>C39</f>
         <v>165.65217391304347</v>
       </c>
-      <c r="D32" s="8">
-        <f t="shared" si="2"/>
-        <v>171.17391304347825</v>
-      </c>
-      <c r="E32" s="8">
+      <c r="D32" s="7">
         <f t="shared" si="2"/>
         <v>173.93478260869566</v>
       </c>
-      <c r="F32" s="8">
+      <c r="E32" s="7">
         <f t="shared" si="2"/>
         <v>179.45652173913041</v>
       </c>
-      <c r="G32" s="8">
+      <c r="F32" s="7">
         <f t="shared" si="2"/>
         <v>184.97826086956522</v>
       </c>
-      <c r="H32" s="8">
+      <c r="G32" s="7">
         <f t="shared" si="2"/>
         <v>187.7391304347826</v>
       </c>
-      <c r="I32" s="8">
+      <c r="H32" s="7">
         <f t="shared" si="2"/>
         <v>193.2608695652174</v>
       </c>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C33" s="5" t="s">
         <v>98</v>
       </c>
@@ -1657,14 +1667,11 @@
       <c r="H33" t="s">
         <v>103</v>
       </c>
-      <c r="I33" t="s">
-        <v>104</v>
-      </c>
-      <c r="J33" s="6" t="s">
+      <c r="I33" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>30</v>
       </c>
@@ -1678,22 +1685,19 @@
         <v>29</v>
       </c>
       <c r="E34" s="2">
-        <v>29</v>
-      </c>
-      <c r="F34" s="1">
         <v>31</v>
       </c>
+      <c r="F34" s="2">
+        <v>32</v>
+      </c>
       <c r="G34" s="2">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H34" s="2">
-        <v>32.5</v>
-      </c>
-      <c r="I34" s="2">
         <v>33.5</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -1704,25 +1708,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="2">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="E35" s="2">
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
       <c r="F35" s="2">
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
       <c r="G35" s="2">
-        <v>33.5</v>
-      </c>
-      <c r="H35" s="2">
         <v>34</v>
       </c>
-      <c r="I35" s="2">
+      <c r="H35" s="13">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1734,31 +1735,27 @@
         <v>71.12</v>
       </c>
       <c r="D36" s="2">
-        <f t="shared" ref="D36:I37" si="3">D34*2.54</f>
+        <f t="shared" ref="D36:H37" si="3">D34*2.54</f>
         <v>73.66</v>
       </c>
       <c r="E36" s="2">
         <f t="shared" si="3"/>
-        <v>73.66</v>
+        <v>78.739999999999995</v>
       </c>
       <c r="F36" s="2">
         <f t="shared" si="3"/>
-        <v>78.739999999999995</v>
+        <v>81.28</v>
       </c>
       <c r="G36" s="2">
         <f t="shared" si="3"/>
-        <v>81.28</v>
+        <v>82.55</v>
       </c>
       <c r="H36" s="2">
         <f t="shared" si="3"/>
-        <v>82.55</v>
-      </c>
-      <c r="I36" s="2">
-        <f t="shared" si="3"/>
         <v>85.09</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -1771,30 +1768,26 @@
       </c>
       <c r="D37" s="2">
         <f t="shared" si="3"/>
-        <v>78.739999999999995</v>
+        <v>80.010000000000005</v>
       </c>
       <c r="E37" s="2">
         <f t="shared" si="3"/>
-        <v>80.010000000000005</v>
+        <v>82.55</v>
       </c>
       <c r="F37" s="2">
         <f t="shared" si="3"/>
-        <v>82.55</v>
+        <v>85.09</v>
       </c>
       <c r="G37" s="2">
         <f t="shared" si="3"/>
-        <v>85.09</v>
+        <v>86.36</v>
       </c>
       <c r="H37" s="2">
         <f t="shared" si="3"/>
-        <v>86.36</v>
-      </c>
-      <c r="I37" s="2">
-        <f t="shared" si="3"/>
         <v>88.9</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -1806,31 +1799,27 @@
         <v>154.60869565217391</v>
       </c>
       <c r="D38" s="2">
-        <f t="shared" ref="D38:I39" si="4">D36/0.46</f>
+        <f t="shared" ref="D38:H39" si="4">D36/0.46</f>
         <v>160.13043478260869</v>
       </c>
       <c r="E38" s="2">
         <f t="shared" si="4"/>
-        <v>160.13043478260869</v>
+        <v>171.17391304347825</v>
       </c>
       <c r="F38" s="2">
         <f t="shared" si="4"/>
-        <v>171.17391304347825</v>
+        <v>176.69565217391303</v>
       </c>
       <c r="G38" s="2">
         <f t="shared" si="4"/>
-        <v>176.69565217391303</v>
+        <v>179.45652173913041</v>
       </c>
       <c r="H38" s="2">
         <f t="shared" si="4"/>
-        <v>179.45652173913041</v>
-      </c>
-      <c r="I38" s="2">
-        <f>I36/0.46</f>
         <v>184.97826086956522</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -1841,30 +1830,26 @@
       </c>
       <c r="D39" s="2">
         <f t="shared" si="4"/>
-        <v>171.17391304347825</v>
+        <v>173.93478260869566</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="4"/>
-        <v>173.93478260869566</v>
+        <v>179.45652173913041</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" si="4"/>
-        <v>179.45652173913041</v>
+        <v>184.97826086956522</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="4"/>
-        <v>184.97826086956522</v>
+        <v>187.7391304347826</v>
       </c>
       <c r="H39" s="2">
         <f t="shared" si="4"/>
-        <v>187.7391304347826</v>
-      </c>
-      <c r="I39" s="2">
-        <f t="shared" si="4"/>
         <v>193.2608695652174</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>35</v>
       </c>
@@ -1875,7 +1860,7 @@
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>36</v>
       </c>
@@ -1886,7 +1871,7 @@
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -1897,7 +1882,7 @@
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -1908,22 +1893,22 @@
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>42</v>
       </c>
@@ -1931,7 +1916,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>43</v>
       </c>
@@ -1941,32 +1926,41 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="B49">
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>115</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>116</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -2020,6 +2014,9 @@
       <c r="A62" t="s">
         <v>50</v>
       </c>
+      <c r="B62">
+        <v>180</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -2112,7 +2109,7 @@
         <v>64</v>
       </c>
       <c r="B75">
-        <v>2099</v>
+        <v>2649</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>92</v>
@@ -2138,10 +2135,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Binary Kinetik 2025.xlsx
+++ b/data/gravel/Binary Kinetik 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A201B27D-9C30-FB44-8788-9EDBD21DFA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B37BA5-C681-4243-B864-2E30D230B7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32940" yWindow="-22820" windowWidth="28300" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="133">
   <si>
     <t>brand</t>
   </si>
@@ -86,9 +86,6 @@
     <t>fork_offset_rake</t>
   </si>
   <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>wheelbase</t>
   </si>
   <si>
@@ -254,9 +251,6 @@
     <t>frame_weight</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -425,10 +419,19 @@
     <t>EC44</t>
   </si>
   <si>
-    <t>a8:h32</t>
-  </si>
-  <si>
     <t>SMD</t>
+  </si>
+  <si>
+    <t>fork travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>suspension</t>
+  </si>
+  <si>
+    <t>a8:h33</t>
   </si>
 </sst>
 </file>
@@ -839,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W79"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -850,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
@@ -858,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -882,12 +885,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -895,7 +898,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="21" x14ac:dyDescent="0.3">
@@ -903,25 +906,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -942,7 +945,7 @@
         <v>13</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="9">
         <v>593</v>
@@ -963,28 +966,28 @@
         <v>651</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="S9" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="R9" s="10" t="s">
+      <c r="T9" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="S9" s="10" t="s">
+      <c r="U9" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="T9" s="10" t="s">
+      <c r="V9" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="U9" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="V9" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="W9" s="11"/>
     </row>
@@ -993,7 +996,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C10" s="9">
         <v>390</v>
@@ -1022,25 +1025,25 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S10" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T10" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="U10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="V10" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="U10" s="8" t="s">
+      <c r="W10" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="V10" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="W10" s="8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="21" x14ac:dyDescent="0.3">
@@ -1048,7 +1051,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" s="9">
         <v>74</v>
@@ -1082,7 +1085,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="9">
         <v>100</v>
@@ -1116,7 +1119,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" s="9">
         <v>67</v>
@@ -1150,7 +1153,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C14" s="9">
         <v>60</v>
@@ -1184,7 +1187,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" s="9">
         <f>VALUE(LEFT(I15,3))</f>
@@ -1211,33 +1214,33 @@
         <v>455</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="21" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C16" s="9">
         <v>512</v>
@@ -1258,7 +1261,7 @@
         <v>512</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J16" s="1"/>
     </row>
@@ -1267,7 +1270,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C17" s="9">
         <f>VALUE(LEFT(I17,2))</f>
@@ -1294,33 +1297,33 @@
         <v>44</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C18" s="9">
         <v>1151</v>
@@ -1348,10 +1351,10 @@
     </row>
     <row r="19" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" s="9">
         <v>616</v>
@@ -1374,10 +1377,10 @@
     </row>
     <row r="20" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" s="9">
         <v>417</v>
@@ -1400,10 +1403,10 @@
     </row>
     <row r="21" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C21" s="9">
         <v>703</v>
@@ -1426,10 +1429,10 @@
     </row>
     <row r="22" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="9">
         <v>771</v>
@@ -1450,19 +1453,33 @@
         <v>887</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
+    <row r="23" spans="1:15" ht="21" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9">
+        <v>120</v>
+      </c>
+      <c r="D23" s="9">
+        <v>120</v>
+      </c>
+      <c r="E23" s="9">
+        <v>120</v>
+      </c>
+      <c r="F23" s="9">
+        <v>120</v>
+      </c>
+      <c r="G23" s="9">
+        <v>120</v>
+      </c>
+      <c r="H23" s="9">
+        <v>120</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -1471,8 +1488,8 @@
       <c r="M24" s="3"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -1492,7 +1509,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -1502,25 +1519,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28">
-        <v>700</v>
-      </c>
-      <c r="D28">
-        <v>700</v>
-      </c>
-      <c r="E28">
-        <v>700</v>
-      </c>
-      <c r="F28">
-        <v>700</v>
-      </c>
-      <c r="G28">
-        <v>700</v>
-      </c>
-      <c r="H28">
-        <v>700</v>
+        <v>24</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -1530,25 +1529,25 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>700</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>700</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>700</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>700</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>700</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <v>700</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -1558,7 +1557,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -1586,31 +1585,25 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="7">
-        <f>C38</f>
-        <v>154.60869565217391</v>
-      </c>
-      <c r="D31" s="7">
-        <f t="shared" ref="D31:H32" si="2">D38</f>
-        <v>160.13043478260869</v>
-      </c>
-      <c r="E31" s="7">
-        <f t="shared" si="2"/>
-        <v>171.17391304347825</v>
-      </c>
-      <c r="F31" s="7">
-        <f t="shared" si="2"/>
-        <v>176.69565217391303</v>
-      </c>
-      <c r="G31" s="7">
-        <f t="shared" si="2"/>
-        <v>179.45652173913041</v>
-      </c>
-      <c r="H31" s="7">
-        <f t="shared" si="2"/>
-        <v>184.97826086956522</v>
+        <v>26</v>
+      </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31">
+        <v>3</v>
+      </c>
+      <c r="H31">
+        <v>3</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -1620,252 +1613,275 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C32" s="7">
         <f>C39</f>
+        <v>154.60869565217391</v>
+      </c>
+      <c r="D32" s="7">
+        <f t="shared" ref="D32:H33" si="2">D39</f>
+        <v>160.13043478260869</v>
+      </c>
+      <c r="E32" s="7">
+        <f t="shared" si="2"/>
+        <v>171.17391304347825</v>
+      </c>
+      <c r="F32" s="7">
+        <f t="shared" si="2"/>
+        <v>176.69565217391303</v>
+      </c>
+      <c r="G32" s="7">
+        <f t="shared" si="2"/>
+        <v>179.45652173913041</v>
+      </c>
+      <c r="H32" s="7">
+        <f t="shared" si="2"/>
+        <v>184.97826086956522</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="7">
+        <f>C40</f>
         <v>165.65217391304347</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D33" s="7">
         <f t="shared" si="2"/>
         <v>173.93478260869566</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E33" s="7">
         <f t="shared" si="2"/>
         <v>179.45652173913041</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F33" s="7">
         <f t="shared" si="2"/>
         <v>184.97826086956522</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G33" s="7">
         <f t="shared" si="2"/>
         <v>187.7391304347826</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H33" s="7">
         <f t="shared" si="2"/>
         <v>193.2608695652174</v>
       </c>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="5" t="s">
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="F34" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="H34" t="s">
         <v>101</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="H33" t="s">
-        <v>103</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="2">
-        <v>28</v>
-      </c>
-      <c r="D34" s="2">
-        <v>29</v>
-      </c>
-      <c r="E34" s="2">
-        <v>31</v>
-      </c>
-      <c r="F34" s="2">
-        <v>32</v>
-      </c>
-      <c r="G34" s="2">
-        <v>32.5</v>
-      </c>
-      <c r="H34" s="2">
-        <v>33.5</v>
+      <c r="I34" s="6" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="C35" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D35" s="2">
-        <v>31.5</v>
+        <v>29</v>
       </c>
       <c r="E35" s="2">
+        <v>31</v>
+      </c>
+      <c r="F35" s="2">
+        <v>32</v>
+      </c>
+      <c r="G35" s="2">
         <v>32.5</v>
       </c>
-      <c r="F35" s="2">
+      <c r="H35" s="2">
         <v>33.5</v>
-      </c>
-      <c r="G35" s="2">
-        <v>34</v>
-      </c>
-      <c r="H35" s="13">
-        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>109</v>
+        <v>67</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
       </c>
       <c r="C36" s="2">
-        <f>C34*2.54</f>
+        <v>30</v>
+      </c>
+      <c r="D36" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="E36" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="F36" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="G36" s="2">
+        <v>34</v>
+      </c>
+      <c r="H36" s="13">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="2">
+        <f>C35*2.54</f>
         <v>71.12</v>
       </c>
-      <c r="D36" s="2">
-        <f t="shared" ref="D36:H37" si="3">D34*2.54</f>
+      <c r="D37" s="2">
+        <f t="shared" ref="D37:H38" si="3">D35*2.54</f>
         <v>73.66</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E37" s="2">
         <f t="shared" si="3"/>
         <v>78.739999999999995</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F37" s="2">
         <f t="shared" si="3"/>
         <v>81.28</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G37" s="2">
         <f t="shared" si="3"/>
         <v>82.55</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H37" s="2">
         <f t="shared" si="3"/>
         <v>85.09</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="2">
-        <f>C35*2.54</f>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="2">
+        <f>C36*2.54</f>
         <v>76.2</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D38" s="2">
         <f t="shared" si="3"/>
         <v>80.010000000000005</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E38" s="2">
         <f t="shared" si="3"/>
         <v>82.55</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F38" s="2">
         <f t="shared" si="3"/>
         <v>85.09</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G38" s="2">
         <f t="shared" si="3"/>
         <v>86.36</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H38" s="2">
         <f t="shared" si="3"/>
         <v>88.9</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="2">
-        <f>C36/0.46</f>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="2">
+        <f>C37/0.46</f>
         <v>154.60869565217391</v>
       </c>
-      <c r="D38" s="2">
-        <f t="shared" ref="D38:H39" si="4">D36/0.46</f>
+      <c r="D39" s="2">
+        <f t="shared" ref="D39:H40" si="4">D37/0.46</f>
         <v>160.13043478260869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E39" s="2">
         <f t="shared" si="4"/>
         <v>171.17391304347825</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F39" s="2">
         <f t="shared" si="4"/>
         <v>176.69565217391303</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G39" s="2">
         <f t="shared" si="4"/>
         <v>179.45652173913041</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H39" s="2">
         <f t="shared" si="4"/>
         <v>184.97826086956522</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>33</v>
-      </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="2">
-        <f>C37/0.46</f>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="2">
+        <f>C38/0.46</f>
         <v>165.65217391304347</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D40" s="2">
         <f t="shared" si="4"/>
         <v>173.93478260869566</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E40" s="2">
         <f t="shared" si="4"/>
         <v>179.45652173913041</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F40" s="2">
         <f t="shared" si="4"/>
         <v>184.97826086956522</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G40" s="2">
         <f t="shared" si="4"/>
         <v>187.7391304347826</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H40" s="2">
         <f t="shared" si="4"/>
         <v>193.2608695652174</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" s="1">
-        <v>17</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-    </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41">
-        <v>3</v>
+        <v>34</v>
+      </c>
+      <c r="B41" s="1">
+        <v>17</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -1873,7 +1889,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B42">
         <v>3</v>
@@ -1884,10 +1900,10 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B43">
-        <v>120</v>
+        <v>3</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -1895,181 +1911,187 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>39</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B44">
+        <v>120</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="B45">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47">
-        <v>148</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B48">
-        <v>110</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>42</v>
       </c>
       <c r="B49">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>115</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>128</v>
+        <v>112</v>
+      </c>
+      <c r="B50">
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>117</v>
+        <v>114</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57">
-        <v>31.6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
+      </c>
+      <c r="B58">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>47</v>
-      </c>
-      <c r="B59">
-        <v>38</v>
+        <v>54</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="B60">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>50</v>
-      </c>
-      <c r="B62">
-        <v>180</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>51</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B63">
+        <v>180</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>95</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="B64" s="1"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -2077,68 +2099,76 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>64</v>
-      </c>
-      <c r="B75">
-        <v>2649</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>92</v>
+        <v>62</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>63</v>
+      </c>
+      <c r="B76">
+        <v>2649</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>67</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>112</v>
-      </c>
-      <c r="B79" t="s">
-        <v>113</v>
+        <v>66</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Binary Kinetik 2025.xlsx
+++ b/data/gravel/Binary Kinetik 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B37BA5-C681-4243-B864-2E30D230B7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB07B4E3-B10C-F14D-9030-8EA53D89AAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -422,9 +422,6 @@
     <t>SMD</t>
   </si>
   <si>
-    <t>fork travel</t>
-  </si>
-  <si>
     <t>fork_sag</t>
   </si>
   <si>
@@ -432,6 +429,9 @@
   </si>
   <si>
     <t>a8:h33</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
   </si>
 </sst>
 </file>
@@ -898,7 +898,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="21" x14ac:dyDescent="0.3">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="23" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B23" s="9"/>
       <c r="C23" s="9">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -1787,7 +1787,7 @@
         <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C38" s="2">
         <f>C36*2.54</f>
